--- a/data.xlsx
+++ b/data.xlsx
@@ -1,26 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29819"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kevin\Downloads\Desalination Project Vibe Code\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kevin\Downloads\Desalination Project Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E965BD07-92FC-454E-A8DE-A2FF0C234EEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{401DE784-F3C2-460A-A449-180827C0AD8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="1" activeTab="1" xr2:uid="{4D6F2CCD-3882-4748-8508-2817CBEB5436}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Part 1" sheetId="1" r:id="rId1"/>
     <sheet name="Part 2" sheetId="2" r:id="rId2"/>
+    <sheet name="Energy" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -37,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="96">
   <si>
     <t>Electrical Components</t>
   </si>
@@ -45,139 +43,151 @@
     <t>Quantity</t>
   </si>
   <si>
+    <t>Unit Cost (USD)</t>
+  </si>
+  <si>
+    <t>Total Cost</t>
+  </si>
+  <si>
+    <t>1.5 MW Turbine (GE Vernova 1.5sle)</t>
+  </si>
+  <si>
+    <t>PLC (Siemens SIMATIC S7-1200 CPU1215C-1)</t>
+  </si>
+  <si>
+    <t>Battery Fraction</t>
+  </si>
+  <si>
+    <t>Tank Fraction</t>
+  </si>
+  <si>
+    <t>Battery kWh</t>
+  </si>
+  <si>
+    <t>Tank Gal</t>
+  </si>
+  <si>
+    <t>Battery Cost ($)</t>
+  </si>
+  <si>
+    <t>Tank Cost ($)</t>
+  </si>
+  <si>
+    <t>Total Cost ($)</t>
+  </si>
+  <si>
+    <t>Submersible Pumps (WDM (Nidec) NHE Series high-head submersible)</t>
+  </si>
+  <si>
+    <t>Battery (Tesla Megapack 3.9MWh unit)</t>
+  </si>
+  <si>
+    <t>Booster Pumps (Grundfos CR 10-10 K)</t>
+  </si>
+  <si>
+    <t>RO Membrane Trains</t>
+  </si>
+  <si>
+    <t>Calcite Bed Contactor (DrinTec FRP Calcite Contactor)</t>
+  </si>
+  <si>
+    <t>Multi-Media Filtration System (Pure Aqua MF-500 Series FRP Filter Skid)</t>
+  </si>
+  <si>
+    <t>Brine Disposal Well</t>
+  </si>
+  <si>
+    <t>Piping (total)</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Mechanical Components</t>
+  </si>
+  <si>
     <t>Cost (USD)</t>
   </si>
   <si>
-    <t xml:space="preserve">Energy kW </t>
-  </si>
-  <si>
-    <t>Land Area (m^2)</t>
-  </si>
-  <si>
-    <t>Lifespan (years)</t>
-  </si>
-  <si>
-    <t>Turbine</t>
-  </si>
-  <si>
-    <t>PLC</t>
-  </si>
-  <si>
-    <t>Battery Fraction</t>
-  </si>
-  <si>
-    <t>Tank Fraction</t>
-  </si>
-  <si>
-    <t>Battery kWh</t>
-  </si>
-  <si>
-    <t>Tank Gal</t>
-  </si>
-  <si>
-    <t>Battery Cost ($)</t>
-  </si>
-  <si>
-    <t>Tank Cost ($)</t>
-  </si>
-  <si>
-    <t>Total Cost ($)</t>
-  </si>
-  <si>
-    <t>Submersible pump</t>
-  </si>
-  <si>
-    <t>Battery (1 day of power)</t>
-  </si>
-  <si>
-    <t>Booster Pump</t>
-  </si>
-  <si>
-    <t>RO membranes in parallel</t>
+    <t>1 MW Aeromotor Turbine</t>
+  </si>
+  <si>
+    <t>Wind turbine rotor lock</t>
+  </si>
+  <si>
+    <t>Gearbox (Winergy  PEAB series)</t>
+  </si>
+  <si>
+    <t>Variable-Displacement Hydraulic Power Unit (HPU)</t>
+  </si>
+  <si>
+    <t>Note: likely will not be COTS, need custom engineering solutions for this scale</t>
+  </si>
+  <si>
+    <t>300 Bar Hydraulic Manifold (Custom Ductile Iron Block)</t>
+  </si>
+  <si>
+    <t>Hydraulic Motor (225 kW rating) (Haaglund CA 50)</t>
+  </si>
+  <si>
+    <t>Hydraulic Motor (225 kW rating) (Haaglund CA 70)</t>
+  </si>
+  <si>
+    <t>Vertical Turbine Pump (PSI Prolew Flowserve VTP)</t>
+  </si>
+  <si>
+    <t>Plunger Pump (Triplex Plunger Pump K 13000 – 3G)</t>
+  </si>
+  <si>
+    <t>High Pressure Pump (Danfoss APP 78/1500 180B7808 (1300 L/min)</t>
+  </si>
+  <si>
+    <t>Gate valve</t>
+  </si>
+  <si>
+    <t>Reverse osmosis train</t>
+  </si>
+  <si>
+    <t>Extra storage tank (100,000 gallons)</t>
   </si>
   <si>
     <t>Calcite bed contactors</t>
   </si>
   <si>
-    <t>Multi-Media Filtration</t>
-  </si>
-  <si>
-    <t>Brine Well</t>
-  </si>
-  <si>
-    <t>indefinite</t>
-  </si>
-  <si>
     <t>Pipes (total)</t>
   </si>
   <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Mechanical Components</t>
-  </si>
-  <si>
-    <t>Energy kW</t>
-  </si>
-  <si>
-    <t>Land Area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">250kW aeromotor turbine </t>
-  </si>
-  <si>
-    <t>2 RO membranes in parallel</t>
-  </si>
-  <si>
-    <t>Pipes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Submersible pump </t>
-  </si>
-  <si>
-    <t>Wind turbine rotor lock</t>
-  </si>
-  <si>
-    <t>Extra storage tank</t>
-  </si>
-  <si>
-    <t>Gate valve</t>
-  </si>
-  <si>
-    <t>Gear and Booster Pump</t>
-  </si>
-  <si>
-    <t>Miscalleneous</t>
-  </si>
-  <si>
-    <t>Green blend addition</t>
-  </si>
-  <si>
-    <t>Activated carbon (annual)</t>
-  </si>
-  <si>
-    <t>~15 tons</t>
-  </si>
-  <si>
-    <t>$ 2500 per ton</t>
-  </si>
-  <si>
-    <t>Evaporation Pond</t>
-  </si>
-  <si>
-    <t>Piston pump</t>
-  </si>
-  <si>
-    <t>Antiscalant (assuming 3g/L of antiscalant)</t>
-  </si>
-  <si>
-    <t>$50000/year</t>
-  </si>
-  <si>
-    <t>~9 containers per year</t>
-  </si>
-  <si>
-    <t>55 gallon container is 2500 USD, for 1 million gal/day lasts about 20 days</t>
+    <t>Hybrid Components</t>
+  </si>
+  <si>
+    <t>Gearbox (Winergy PEAB series)</t>
+  </si>
+  <si>
+    <t>Variable-Displacement HPU</t>
+  </si>
+  <si>
+    <t>Hydraulic Motor (225 kW, Haaglund CA 50)</t>
+  </si>
+  <si>
+    <t>High Pressure Pump (Danfoss APP 78/1500 180B7808)</t>
+  </si>
+  <si>
+    <t>Battery (Tesla Megapack 3.9 MWh)</t>
+  </si>
+  <si>
+    <t>Booster Pump (Grundfos CR 10-10 K)</t>
+  </si>
+  <si>
+    <t>PLC (Siemens SIMATIC S7-1200 CPU1215C-1)</t>
+  </si>
+  <si>
+    <t>Multi-Media Filtration System (Pure Aqua MF-500 Series)</t>
+  </si>
+  <si>
+    <t>Reverse Osmosis Trains</t>
+  </si>
+  <si>
+    <t>Extra Storage Tank (100,000 gallons)</t>
   </si>
   <si>
     <t>TDS</t>
@@ -190,6 +200,129 @@
   </si>
   <si>
     <t>kW required (pump energy)</t>
+  </si>
+  <si>
+    <t>System / Subsystem</t>
+  </si>
+  <si>
+    <t>Shaft Power (kW)</t>
+  </si>
+  <si>
+    <t>Drive Type</t>
+  </si>
+  <si>
+    <t>Drivetrain Efficiency</t>
+  </si>
+  <si>
+    <t>Turbine Input (kW)</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Mechanical System</t>
+  </si>
+  <si>
+    <t>GW Extraction (Vertical Turbine Pump)</t>
+  </si>
+  <si>
+    <t>Hydraulic</t>
+  </si>
+  <si>
+    <t>hm x hpu x gb = 0.768</t>
+  </si>
+  <si>
+    <t>VTP driven by dedicated hydraulic motor</t>
+  </si>
+  <si>
+    <t>RO Feed Pressurization (High Pressure Pump)</t>
+  </si>
+  <si>
+    <t>Danfoss APP x3 driven by hydraulic motor</t>
+  </si>
+  <si>
+    <t>Brine Reinjection (Triplex Plunger Pump)</t>
+  </si>
+  <si>
+    <t>Plunger pump driven by hydraulic motor</t>
+  </si>
+  <si>
+    <t>Total Shaft Power</t>
+  </si>
+  <si>
+    <t>Total at Turbine Shaft</t>
+  </si>
+  <si>
+    <t>Design Power (+10% margin)</t>
+  </si>
+  <si>
+    <t>Selected Turbine (kW)</t>
+  </si>
+  <si>
+    <t>850 kW - next standard commercial above 810.8 kW design requirement</t>
+  </si>
+  <si>
+    <t>Electrical System</t>
+  </si>
+  <si>
+    <t>GW Extraction (Submersible Pump)</t>
+  </si>
+  <si>
+    <t>Electric motor</t>
+  </si>
+  <si>
+    <t>h_motor = 0.95</t>
+  </si>
+  <si>
+    <t>VFD-driven submersible; no HPU or gearbox losses</t>
+  </si>
+  <si>
+    <t>RO Feed Pressurization (Booster Pump)</t>
+  </si>
+  <si>
+    <t>Grundfos CR multi-stage; direct electric drive</t>
+  </si>
+  <si>
+    <t>Brine Disposal (Electric Pump to Well)</t>
+  </si>
+  <si>
+    <t>Electric pump to brine disposal well</t>
+  </si>
+  <si>
+    <t>Total Electrical Demand</t>
+  </si>
+  <si>
+    <t>Hybrid System</t>
+  </si>
+  <si>
+    <t>RO Feed Pressurization - hydraulic path (HP Pump)</t>
+  </si>
+  <si>
+    <t>HPU + hydraulic motor drives HP pump; highest-power load on hydraulic path</t>
+  </si>
+  <si>
+    <t>GW Extraction - electrical path (VTP)</t>
+  </si>
+  <si>
+    <t>h_motor x h_gen = 0.95 x 0.95 = 0.903</t>
+  </si>
+  <si>
+    <t>Turbine generator -&gt; battery -&gt; VTP motor</t>
+  </si>
+  <si>
+    <t>Brine Disposal - electrical path</t>
+  </si>
+  <si>
+    <t>Turbine generator -&gt; battery -&gt; disposal pump</t>
+  </si>
+  <si>
+    <t>Total at Turbine (hydraulic + electrical paths)</t>
+  </si>
+  <si>
+    <t>850 kW - same commercial platform as mechanical for consistency</t>
+  </si>
+  <si>
+    <t>1.5 MW GE Vernova 1.5sle - excess capacity charges battery for 24/7 continuous operations</t>
   </si>
 </sst>
 </file>
@@ -199,7 +332,7 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -252,8 +385,74 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -268,12 +467,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC0E6F5"/>
-        <bgColor rgb="FFC0E6F5"/>
+        <fgColor rgb="FF156082"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6E4F0"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -282,79 +485,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF44B3E1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF44B3E1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF44B3E1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="FF44B3E1"/>
+        <color theme="4" tint="0.39997558519241921"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF44B3E1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF44B3E1"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF44B3E1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF44B3E1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF44B3E1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF44B3E1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF44B3E1"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF44B3E1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF44B3E1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF44B3E1"/>
+        <color theme="4" tint="0.39997558519241921"/>
       </bottom>
       <diagonal/>
     </border>
@@ -362,36 +499,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="8" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="8" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="8" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="8" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="8" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="8" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="8" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="8" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="8" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="8" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -725,26 +861,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EB37D88-D019-4C24-B43B-C69173A467AF}">
-  <dimension ref="A1:P33"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:R50"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="19.28515625" customWidth="1"/>
-    <col min="3" max="3" width="21.5703125" customWidth="1"/>
-    <col min="4" max="4" width="25.140625" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" customWidth="1"/>
-    <col min="7" max="7" width="21.7109375" customWidth="1"/>
-    <col min="10" max="10" width="13.85546875" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" customWidth="1"/>
-    <col min="14" max="14" width="16.140625" customWidth="1"/>
-    <col min="15" max="15" width="13.140625" customWidth="1"/>
-    <col min="16" max="16" width="10.5703125" customWidth="1"/>
+    <col min="2" max="2" width="59.26953125" customWidth="1"/>
+    <col min="3" max="3" width="21.54296875" customWidth="1"/>
+    <col min="4" max="4" width="25.1796875" customWidth="1"/>
+    <col min="5" max="5" width="16.1796875" customWidth="1"/>
+    <col min="6" max="6" width="14.81640625" customWidth="1"/>
+    <col min="7" max="7" width="21.7265625" customWidth="1"/>
+    <col min="12" max="12" width="13.81640625" customWidth="1"/>
+    <col min="13" max="13" width="14.54296875" customWidth="1"/>
+    <col min="14" max="14" width="14.81640625" customWidth="1"/>
+    <col min="15" max="15" width="13.453125" customWidth="1"/>
+    <col min="16" max="16" width="16.1796875" customWidth="1"/>
+    <col min="17" max="17" width="13.1796875" customWidth="1"/>
+    <col min="18" max="18" width="10.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:18" ht="20.25" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -758,449 +894,390 @@
       <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:18" ht="14.5">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" s="1"/>
-      <c r="B2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="3">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4">
-        <v>1500000</v>
-      </c>
-      <c r="E2" s="3">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3">
-        <v>500</v>
-      </c>
-      <c r="G2" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="C2" s="16">
+        <v>1</v>
+      </c>
+      <c r="D2" s="8">
+        <v>1000000</v>
+      </c>
+      <c r="E2" s="17">
+        <f t="shared" ref="E2:E11" si="0">D2*C2</f>
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="15.75" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="16">
+        <v>2</v>
+      </c>
+      <c r="D3" s="8">
+        <v>2600</v>
+      </c>
+      <c r="E3" s="17">
+        <f t="shared" si="0"/>
+        <v>5200</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="1">
-        <v>1</v>
-      </c>
-      <c r="D3" s="5">
-        <v>2000</v>
-      </c>
-      <c r="E3" s="1">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1">
-        <v>7</v>
-      </c>
-      <c r="G3" s="1">
+      <c r="N3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="P3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="M3" s="7" t="s">
+      <c r="Q3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="R3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="O3" s="7" t="s">
+    </row>
+    <row r="4" spans="1:18" ht="14.5">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="P3" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="A4" s="1"/>
-      <c r="B4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="3">
+      <c r="C4" s="16">
         <v>2</v>
       </c>
-      <c r="D4" s="6">
-        <v>24266</v>
-      </c>
-      <c r="E4" s="3">
-        <v>196.64</v>
-      </c>
-      <c r="F4" s="3">
-        <v>25</v>
-      </c>
-      <c r="G4" s="3">
-        <v>20</v>
-      </c>
-      <c r="J4" s="1">
-        <v>0</v>
-      </c>
-      <c r="K4" s="1">
-        <v>1</v>
+      <c r="D4" s="9">
+        <v>200000</v>
+      </c>
+      <c r="E4" s="17">
+        <f t="shared" si="0"/>
+        <v>400000</v>
       </c>
       <c r="L4" s="1">
         <v>0</v>
       </c>
-      <c r="M4" s="21">
-        <v>1000000</v>
+      <c r="M4" s="1">
+        <v>1</v>
       </c>
       <c r="N4" s="1">
         <v>0</v>
       </c>
-      <c r="O4" s="21">
+      <c r="O4" s="4">
+        <v>1000000</v>
+      </c>
+      <c r="P4" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="4">
         <v>150000</v>
       </c>
-      <c r="P4" s="21">
+      <c r="R4" s="4">
         <v>150000</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:18" ht="14.5">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="1">
-        <v>1</v>
-      </c>
-      <c r="D5" s="5">
-        <v>1800000</v>
-      </c>
-      <c r="E5" s="1">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1">
-        <v>150</v>
-      </c>
-      <c r="G5" s="1">
-        <v>12</v>
-      </c>
-      <c r="J5" s="1">
+        <v>14</v>
+      </c>
+      <c r="C5" s="16">
+        <v>1</v>
+      </c>
+      <c r="D5" s="9">
+        <v>2600000</v>
+      </c>
+      <c r="E5" s="17">
+        <f t="shared" si="0"/>
+        <v>2600000</v>
+      </c>
+      <c r="L5" s="1">
         <v>0.1</v>
       </c>
-      <c r="K5" s="1">
+      <c r="M5" s="1">
         <v>0.9</v>
       </c>
-      <c r="L5" s="21">
+      <c r="N5" s="4">
         <v>1000</v>
       </c>
-      <c r="M5" s="21">
+      <c r="O5" s="4">
         <v>900000</v>
       </c>
-      <c r="N5" s="21">
+      <c r="P5" s="4">
         <v>125000</v>
       </c>
-      <c r="O5" s="21">
+      <c r="Q5" s="4">
         <v>135000</v>
       </c>
-      <c r="P5" s="21">
+      <c r="R5" s="4">
         <v>260000</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:18" ht="14.5">
       <c r="A6" s="1"/>
-      <c r="B6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="3">
+      <c r="B6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="16">
         <v>4</v>
       </c>
-      <c r="D6" s="4">
-        <v>34000</v>
-      </c>
-      <c r="E6" s="3">
-        <v>51.152999999999999</v>
-      </c>
-      <c r="F6" s="3">
-        <v>15</v>
-      </c>
-      <c r="G6" s="3">
-        <v>12</v>
-      </c>
-      <c r="J6" s="1">
+      <c r="D6" s="9">
+        <v>6000</v>
+      </c>
+      <c r="E6" s="17">
+        <f t="shared" si="0"/>
+        <v>24000</v>
+      </c>
+      <c r="L6" s="1">
         <v>0.2</v>
       </c>
-      <c r="K6" s="1">
+      <c r="M6" s="1">
         <v>0.8</v>
       </c>
-      <c r="L6" s="21">
+      <c r="N6" s="4">
         <v>2000</v>
       </c>
-      <c r="M6" s="21">
+      <c r="O6" s="4">
         <v>800000</v>
       </c>
-      <c r="N6" s="21">
+      <c r="P6" s="4">
         <v>250000</v>
       </c>
-      <c r="O6" s="21">
+      <c r="Q6" s="4">
         <v>120000</v>
       </c>
-      <c r="P6" s="21">
+      <c r="R6" s="4">
         <v>370000</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:18" ht="14.5">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="1">
+        <v>16</v>
+      </c>
+      <c r="C7" s="16">
         <v>2</v>
       </c>
-      <c r="D7" s="5">
-        <v>7570000</v>
-      </c>
-      <c r="E7" s="1">
-        <v>311.27</v>
-      </c>
-      <c r="F7" s="1">
-        <v>100</v>
-      </c>
-      <c r="G7" s="1">
-        <v>6</v>
-      </c>
-      <c r="J7" s="1">
+      <c r="D7" s="9">
+        <v>3000000</v>
+      </c>
+      <c r="E7" s="17">
+        <f t="shared" si="0"/>
+        <v>6000000</v>
+      </c>
+      <c r="L7" s="1">
         <v>0.3</v>
       </c>
-      <c r="K7" s="1">
+      <c r="M7" s="1">
         <v>0.7</v>
       </c>
-      <c r="L7" s="21">
+      <c r="N7" s="4">
         <v>3000</v>
       </c>
-      <c r="M7" s="21">
+      <c r="O7" s="4">
         <v>700000</v>
       </c>
-      <c r="N7" s="21">
+      <c r="P7" s="4">
         <v>375000</v>
       </c>
-      <c r="O7" s="21">
+      <c r="Q7" s="4">
         <v>105000</v>
       </c>
-      <c r="P7" s="21">
+      <c r="R7" s="4">
         <v>480000</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:18" ht="14.5">
       <c r="A8" s="1"/>
-      <c r="B8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="3">
-        <v>2</v>
-      </c>
-      <c r="D8" s="4">
-        <v>100000</v>
-      </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>50</v>
-      </c>
-      <c r="G8" s="3">
-        <v>2</v>
-      </c>
-      <c r="J8" s="1">
+      <c r="B8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="16">
+        <v>1</v>
+      </c>
+      <c r="D8" s="9">
+        <v>75000</v>
+      </c>
+      <c r="E8" s="17">
+        <f t="shared" si="0"/>
+        <v>75000</v>
+      </c>
+      <c r="L8" s="1">
         <v>0.4</v>
       </c>
-      <c r="K8" s="1">
+      <c r="M8" s="1">
         <v>0.6</v>
       </c>
-      <c r="L8" s="21">
+      <c r="N8" s="4">
         <v>4000</v>
       </c>
-      <c r="M8" s="21">
+      <c r="O8" s="4">
         <v>600000</v>
       </c>
-      <c r="N8" s="21">
+      <c r="P8" s="4">
         <v>500000</v>
       </c>
-      <c r="O8" s="21">
+      <c r="Q8" s="4">
         <v>90000</v>
       </c>
-      <c r="P8" s="21">
+      <c r="R8" s="4">
         <v>590000</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:18" ht="14.5">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="5">
-        <v>31975</v>
-      </c>
-      <c r="E9" s="1">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1">
-        <v>125</v>
-      </c>
-      <c r="G9" s="1">
-        <v>8</v>
-      </c>
-      <c r="J9" s="1">
+        <v>18</v>
+      </c>
+      <c r="C9" s="16">
+        <v>2</v>
+      </c>
+      <c r="D9" s="9">
+        <v>15000</v>
+      </c>
+      <c r="E9" s="17">
+        <f t="shared" si="0"/>
+        <v>30000</v>
+      </c>
+      <c r="L9" s="1">
         <v>0.5</v>
       </c>
-      <c r="K9" s="1">
+      <c r="M9" s="1">
         <v>0.5</v>
       </c>
-      <c r="L9" s="21">
+      <c r="N9" s="4">
         <v>5000</v>
       </c>
-      <c r="M9" s="21">
+      <c r="O9" s="4">
         <v>500000</v>
       </c>
-      <c r="N9" s="21">
+      <c r="P9" s="4">
         <v>625000</v>
       </c>
-      <c r="O9" s="21">
+      <c r="Q9" s="4">
         <v>75000</v>
       </c>
-      <c r="P9" s="21">
+      <c r="R9" s="4">
         <v>700000</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:18" ht="14.5">
       <c r="A10" s="1"/>
-      <c r="B10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="3">
-        <v>1</v>
-      </c>
-      <c r="D10" s="4">
+      <c r="B10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="16">
+        <v>1</v>
+      </c>
+      <c r="D10" s="9">
         <v>2300000</v>
       </c>
-      <c r="E10" s="3">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3">
-        <v>75</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="J10" s="1">
+      <c r="E10" s="17">
+        <f t="shared" si="0"/>
+        <v>2300000</v>
+      </c>
+      <c r="L10" s="1">
         <v>0.6</v>
       </c>
-      <c r="K10" s="1">
+      <c r="M10" s="1">
         <v>0.4</v>
       </c>
-      <c r="L10" s="21">
+      <c r="N10" s="4">
         <v>6000</v>
       </c>
-      <c r="M10" s="21">
+      <c r="O10" s="4">
         <v>400000</v>
       </c>
-      <c r="N10" s="21">
+      <c r="P10" s="4">
         <v>750000</v>
       </c>
-      <c r="O10" s="21">
+      <c r="Q10" s="4">
         <v>60000</v>
       </c>
-      <c r="P10" s="21">
+      <c r="R10" s="4">
         <v>810000</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:18" ht="14.5">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="1">
-        <v>1</v>
-      </c>
-      <c r="D11" s="5">
+        <v>20</v>
+      </c>
+      <c r="C11" s="16">
+        <v>1</v>
+      </c>
+      <c r="D11" s="9">
         <v>2000000</v>
       </c>
-      <c r="E11" s="1">
-        <v>0</v>
-      </c>
-      <c r="F11" s="1">
-        <v>300</v>
-      </c>
-      <c r="G11" s="1">
-        <v>50</v>
-      </c>
-      <c r="J11" s="1">
+      <c r="E11" s="17">
+        <f t="shared" si="0"/>
+        <v>2000000</v>
+      </c>
+      <c r="L11" s="1">
         <v>0.7</v>
       </c>
-      <c r="K11" s="1">
+      <c r="M11" s="1">
         <v>0.3</v>
       </c>
-      <c r="L11" s="21">
+      <c r="N11" s="4">
         <v>7000</v>
       </c>
-      <c r="M11" s="21">
+      <c r="O11" s="4">
         <v>300000</v>
       </c>
-      <c r="N11" s="21">
+      <c r="P11" s="4">
         <v>875000</v>
       </c>
-      <c r="O11" s="21">
+      <c r="Q11" s="4">
         <v>45000</v>
       </c>
-      <c r="P11" s="21">
+      <c r="R11" s="4">
         <v>920000</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
-      <c r="A12" s="7"/>
-      <c r="B12" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="9">
-        <v>15362241</v>
-      </c>
-      <c r="E12" s="8">
-        <v>559.06299999999999</v>
-      </c>
-      <c r="F12" s="8">
-        <v>1347</v>
-      </c>
-      <c r="G12" s="8"/>
-      <c r="J12" s="1">
+    <row r="12" spans="1:18" ht="14.5">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="18">
+        <f>SUM(E2:E11)</f>
+        <v>14434200</v>
+      </c>
+      <c r="L12" s="1">
         <v>0.8</v>
       </c>
-      <c r="K12" s="1">
+      <c r="M12" s="1">
         <v>0.2</v>
       </c>
-      <c r="L12" s="21">
+      <c r="N12" s="4">
         <v>8000</v>
       </c>
-      <c r="M12" s="21">
+      <c r="O12" s="4">
         <v>200000</v>
       </c>
-      <c r="N12" s="21">
+      <c r="P12" s="4">
         <v>1000000</v>
       </c>
-      <c r="O12" s="21">
+      <c r="Q12" s="4">
         <v>30000</v>
       </c>
-      <c r="P12" s="21">
+      <c r="R12" s="4">
         <v>1030000</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:18" ht="14.5">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -1208,29 +1285,29 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
-      <c r="J13" s="1">
+      <c r="L13" s="1">
         <v>0.9</v>
       </c>
-      <c r="K13" s="1">
+      <c r="M13" s="1">
         <v>0.1</v>
       </c>
-      <c r="L13" s="21">
+      <c r="N13" s="4">
         <v>9000</v>
       </c>
-      <c r="M13" s="21">
+      <c r="O13" s="4">
         <v>100000</v>
       </c>
-      <c r="N13" s="21">
+      <c r="P13" s="4">
         <v>1125000</v>
       </c>
-      <c r="O13" s="21">
+      <c r="Q13" s="4">
         <v>15000</v>
       </c>
-      <c r="P13" s="21">
+      <c r="R13" s="4">
         <v>1140000</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:18" ht="14.5">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1238,429 +1315,512 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
-      <c r="J14" s="1">
-        <v>1</v>
-      </c>
-      <c r="K14" s="1">
-        <v>0</v>
-      </c>
-      <c r="L14" s="21">
-        <v>10000</v>
+      <c r="L14" s="1">
+        <v>1</v>
       </c>
       <c r="M14" s="1">
         <v>0</v>
       </c>
-      <c r="N14" s="21">
-        <v>1250000</v>
+      <c r="N14" s="4">
+        <v>10000</v>
       </c>
       <c r="O14" s="1">
         <v>0</v>
       </c>
-      <c r="P14" s="21">
+      <c r="P14" s="4">
         <v>1250000</v>
       </c>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="Q14" s="1">
+        <v>0</v>
+      </c>
+      <c r="R14" s="4">
+        <v>1250000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="14.5">
       <c r="A15" s="1"/>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="7"/>
+    </row>
+    <row r="16" spans="1:18" ht="14.5">
+      <c r="A16" s="1"/>
+      <c r="B16" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="11">
+        <v>1</v>
+      </c>
+      <c r="D16" s="14">
+        <v>1000000</v>
+      </c>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="1"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.5">
+      <c r="A17" s="1"/>
+      <c r="B17" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="C17" s="11">
+        <v>3</v>
+      </c>
+      <c r="D17" s="14">
+        <v>15000</v>
+      </c>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="1"/>
+    </row>
+    <row r="18" spans="1:7" ht="14.5">
+      <c r="A18" s="1"/>
+      <c r="B18" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="11">
+        <v>1</v>
+      </c>
+      <c r="D18" s="15">
+        <v>200000</v>
+      </c>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="1"/>
+    </row>
+    <row r="19" spans="1:7" ht="14.5">
+      <c r="A19" s="1"/>
+      <c r="B19" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="11">
+        <v>1</v>
+      </c>
+      <c r="D19" s="15">
+        <v>300000</v>
+      </c>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G19" s="1"/>
+    </row>
+    <row r="20" spans="1:7" ht="14.5">
+      <c r="A20" s="1"/>
+      <c r="B20" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="11">
+        <v>1</v>
+      </c>
+      <c r="D20" s="15">
+        <v>20000</v>
+      </c>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" s="1"/>
+    </row>
+    <row r="21" spans="1:7" ht="14.5">
+      <c r="A21" s="1"/>
+      <c r="B21" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="11">
         <v>2</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16">
-      <c r="A16" s="1"/>
-      <c r="B16" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="3">
-        <v>4</v>
-      </c>
-      <c r="D16" s="4">
-        <v>2000000</v>
-      </c>
-      <c r="E16" s="3">
-        <v>0</v>
-      </c>
-      <c r="F16" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G16" s="3">
+      <c r="D21" s="15">
+        <v>60000</v>
+      </c>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="1"/>
+    </row>
+    <row r="22" spans="1:7" ht="14.5">
+      <c r="A22" s="1"/>
+      <c r="B22" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="11">
+        <v>1</v>
+      </c>
+      <c r="D22" s="15">
+        <v>50000</v>
+      </c>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="1"/>
+    </row>
+    <row r="23" spans="1:7" ht="14.5">
+      <c r="A23" s="1"/>
+      <c r="B23" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="11">
+        <v>1</v>
+      </c>
+      <c r="D23" s="15">
+        <v>60000</v>
+      </c>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="1"/>
+    </row>
+    <row r="24" spans="1:7" ht="14.5">
+      <c r="A24" s="1"/>
+      <c r="B24" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="11">
+        <v>1</v>
+      </c>
+      <c r="D24" s="15">
+        <v>35000</v>
+      </c>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="1"/>
+    </row>
+    <row r="25" spans="1:7" ht="14.5">
+      <c r="A25" s="1"/>
+      <c r="B25" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="11">
+        <v>3</v>
+      </c>
+      <c r="D25" s="15">
+        <v>100000</v>
+      </c>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="1"/>
+    </row>
+    <row r="26" spans="1:7" ht="14.5">
+      <c r="A26" s="1"/>
+      <c r="B26" s="11" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="1">
+      <c r="C26" s="11">
         <v>2</v>
       </c>
-      <c r="D17" s="5">
-        <v>7570000</v>
-      </c>
-      <c r="E17" s="1">
-        <v>311.27</v>
-      </c>
-      <c r="F17" s="1">
-        <v>100</v>
-      </c>
-      <c r="G17" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="1"/>
-      <c r="B18" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="4">
-        <v>2000000</v>
-      </c>
-      <c r="E18" s="3">
-        <v>0</v>
-      </c>
-      <c r="F18" s="3">
-        <v>300</v>
-      </c>
-      <c r="G18" s="3">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" s="1">
-        <v>2</v>
-      </c>
-      <c r="D19" s="5">
-        <v>24266</v>
-      </c>
-      <c r="E19" s="1">
-        <v>196.64</v>
-      </c>
-      <c r="F19" s="1">
-        <v>50</v>
-      </c>
-      <c r="G19" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="1"/>
-      <c r="B20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" s="3">
-        <v>3</v>
-      </c>
-      <c r="D20" s="4">
-        <v>15000</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>10</v>
-      </c>
-      <c r="G20" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C21" s="1">
-        <v>2</v>
-      </c>
-      <c r="D21" s="5">
-        <v>140000</v>
-      </c>
-      <c r="E21" s="1">
-        <v>0</v>
-      </c>
-      <c r="F21" s="1">
-        <v>250</v>
-      </c>
-      <c r="G21" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="1"/>
-      <c r="B22" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" s="3">
-        <v>2</v>
-      </c>
-      <c r="D22" s="4">
+      <c r="D26" s="14">
         <v>8000</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>5</v>
-      </c>
-      <c r="G22" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23" s="1">
-        <v>4</v>
-      </c>
-      <c r="D23" s="5">
-        <v>75000</v>
-      </c>
-      <c r="E23" s="1">
-        <v>88.45</v>
-      </c>
-      <c r="F23" s="1">
-        <v>50</v>
-      </c>
-      <c r="G23" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="1"/>
-      <c r="B24" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C24" s="3">
-        <v>2</v>
-      </c>
-      <c r="D24" s="4">
-        <v>100000</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>50</v>
-      </c>
-      <c r="G24" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="10">
-        <v>11932266</v>
-      </c>
-      <c r="E25" s="7">
-        <v>596.36</v>
-      </c>
-      <c r="F25" s="7">
-        <v>1815</v>
-      </c>
-      <c r="G25" s="7"/>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" ht="14.5">
       <c r="A27" s="1"/>
       <c r="B27" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="D27" s="12" t="s">
+      <c r="C27" s="11">
         <v>2</v>
       </c>
-      <c r="E27" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="F27" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="G27" s="13" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+      <c r="D27" s="14">
+        <v>7570000</v>
+      </c>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="1"/>
+    </row>
+    <row r="28" spans="1:7" ht="14.5">
       <c r="A28" s="1"/>
-      <c r="B28" s="14" t="s">
+      <c r="B28" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="11">
         <v>2</v>
       </c>
-      <c r="D28" s="16">
-        <v>226596.13</v>
-      </c>
-      <c r="E28" s="15">
-        <v>0</v>
-      </c>
-      <c r="F28" s="15">
-        <v>100</v>
-      </c>
-      <c r="G28" s="17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+      <c r="D28" s="14">
+        <v>140000</v>
+      </c>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="1"/>
+    </row>
+    <row r="29" spans="1:7" ht="14.5">
       <c r="A29" s="1"/>
-      <c r="B29" s="18" t="s">
+      <c r="B29" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C29" s="19" t="s">
+      <c r="C29" s="11">
+        <v>2</v>
+      </c>
+      <c r="D29" s="14">
+        <v>100000</v>
+      </c>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="1"/>
+    </row>
+    <row r="30" spans="1:7" ht="14.5">
+      <c r="A30" s="3"/>
+      <c r="B30" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="C30" s="11"/>
+      <c r="D30" s="14">
+        <v>2000000</v>
+      </c>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="3"/>
+    </row>
+    <row r="31" spans="1:7" ht="14.5">
+      <c r="A31" s="1"/>
+      <c r="B31" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C31" s="12"/>
+      <c r="D31" s="13">
+        <v>9658000</v>
+      </c>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="1"/>
+    </row>
+    <row r="32" spans="1:7" ht="14.5">
+      <c r="A32" s="1"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="1"/>
+    </row>
+    <row r="33" spans="2:4" ht="14.5">
+      <c r="B33" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="E29" s="19">
-        <v>0</v>
-      </c>
-      <c r="F29" s="19">
-        <v>100</v>
-      </c>
-      <c r="G29" s="20">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="1"/>
-      <c r="B30" s="14" t="s">
+      <c r="C33" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" ht="14.5">
+      <c r="B34" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="19">
+        <v>1</v>
+      </c>
+      <c r="D34" s="19">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" ht="14.5">
+      <c r="B35" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C30" s="15">
-        <v>1</v>
-      </c>
-      <c r="D30" s="16">
-        <v>1000000</v>
-      </c>
-      <c r="E30" s="15">
-        <v>0</v>
-      </c>
-      <c r="F30" s="15">
-        <v>650000</v>
-      </c>
-      <c r="G30" s="17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="1"/>
-      <c r="B31" s="14" t="s">
+      <c r="C35" s="19">
+        <v>1</v>
+      </c>
+      <c r="D35" s="19">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" ht="14.5">
+      <c r="B36" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="C31" s="15">
+      <c r="C36" s="19">
+        <v>1</v>
+      </c>
+      <c r="D36" s="19">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" ht="14.5">
+      <c r="B37" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" s="19">
+        <v>1</v>
+      </c>
+      <c r="D37" s="19">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" ht="14.5">
+      <c r="B38" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="C38" s="19">
+        <v>1</v>
+      </c>
+      <c r="D38" s="19">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" ht="14.5">
+      <c r="B39" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C39" s="19">
+        <v>1</v>
+      </c>
+      <c r="D39" s="19">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" ht="14.5">
+      <c r="B40" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C40" s="19">
+        <v>1</v>
+      </c>
+      <c r="D40" s="19">
+        <v>2600000</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" ht="14.5">
+      <c r="B41" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C41" s="19">
+        <v>1</v>
+      </c>
+      <c r="D41" s="19">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" ht="14.5">
+      <c r="B42" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="C42" s="19">
         <v>2</v>
       </c>
-      <c r="D31" s="16">
-        <v>150000</v>
-      </c>
-      <c r="E31" s="15">
-        <v>102.306</v>
-      </c>
-      <c r="F31" s="15">
+      <c r="D42" s="19">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" ht="14.5">
+      <c r="B43" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C43" s="19">
+        <v>1</v>
+      </c>
+      <c r="D43" s="19">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" ht="14.5">
+      <c r="B44" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="C44" s="19">
+        <v>1</v>
+      </c>
+      <c r="D44" s="19">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" ht="14.5">
+      <c r="B45" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="C45" s="19">
+        <v>2</v>
+      </c>
+      <c r="D45" s="19">
+        <v>7570000</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" ht="14.5">
+      <c r="B46" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C46" s="19">
+        <v>1</v>
+      </c>
+      <c r="D46" s="19">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" ht="14.5">
+      <c r="B47" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C47" s="19">
+        <v>1</v>
+      </c>
+      <c r="D47" s="19">
+        <v>2300000</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" ht="14.5">
+      <c r="B48" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="G31" s="17">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="24"/>
-      <c r="B32" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C32" s="25">
+      <c r="C48" s="19">
         <v>2</v>
       </c>
-      <c r="D32" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="E32" s="25">
-        <v>0</v>
-      </c>
-      <c r="F32" s="25">
-        <v>25</v>
-      </c>
-      <c r="G32" s="26" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="24"/>
-      <c r="B33" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C33" s="27"/>
-      <c r="D33" s="27"/>
-      <c r="E33" s="27"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="28"/>
+      <c r="D48" s="19">
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" ht="14.5">
+      <c r="B49" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C49" s="19"/>
+      <c r="D49" s="19">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" ht="14.5">
+      <c r="B50" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C50" s="20"/>
+      <c r="D50" s="20">
+        <f>SUM(D34:D49)</f>
+        <v>16359600</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="F32:F33"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C39F0B8-8C3B-42AE-9AF7-8CD4FC164E71}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="3" max="3" width="6.81640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="B1" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="D1" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="E1" s="23" t="s">
-        <v>50</v>
+      <c r="A1" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1668,14 +1828,14 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <f>0.0146053*A2 + 630.72</f>
+        <f t="shared" ref="B2:B21" si="0">0.0146053*A2 + 630.72</f>
         <v>630.72</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <f>0.5725*D2</f>
+        <f t="shared" ref="E2:E21" si="1">0.5725*D2</f>
         <v>0</v>
       </c>
     </row>
@@ -1684,14 +1844,14 @@
         <v>100</v>
       </c>
       <c r="B3">
-        <f t="shared" ref="B3:B21" si="0">0.0146053*A3 + 630.72</f>
+        <f t="shared" si="0"/>
         <v>632.18052999999998</v>
       </c>
       <c r="D3">
         <v>100</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E21" si="1">0.5725*D3</f>
+        <f t="shared" si="1"/>
         <v>57.25</v>
       </c>
     </row>
@@ -1986,4 +2146,368 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="54" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="19">
+        <v>172.9</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" s="19">
+        <v>225.1</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="19">
+        <v>311.49</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="19">
+        <v>405.5</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" s="19">
+        <v>81.864999999999995</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" s="19">
+        <v>106.6</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="20">
+        <v>566.255</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="E7" s="20">
+        <v>737.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="20">
+        <v>810.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="E9" s="20">
+        <v>850</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="19">
+        <v>172.9</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="E12" s="19">
+        <v>182</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="19">
+        <v>311.49</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="E13" s="19">
+        <v>327.9</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="19">
+        <v>81.864999999999995</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="E14" s="19">
+        <v>86.2</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="20">
+        <v>566.255</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="E16" s="20">
+        <v>596.1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="20">
+        <v>655.7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" s="20">
+        <v>1500</v>
+      </c>
+      <c r="F18" s="25" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" s="19">
+        <v>311.49</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="E21" s="19">
+        <v>405.5</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" s="19">
+        <v>172.9</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="E22" s="19">
+        <v>191.6</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" s="19">
+        <v>81.864999999999995</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="E23" s="19">
+        <v>90.7</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B24" s="20">
+        <v>566.255</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="E25" s="20">
+        <v>687.7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="E26" s="20">
+        <v>756.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="E27" s="20">
+        <v>850</v>
+      </c>
+      <c r="F27" s="25" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="26"/>
+      <c r="B29" s="27"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="27"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A29:F29"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -1,24 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kevin\Downloads\Desalination Project Code\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kevin\Downloads\Desalination Project Vibe Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{401DE784-F3C2-460A-A449-180827C0AD8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{02C01666-7467-4833-B789-B11D72E586F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{4D6F2CCD-3882-4748-8508-2817CBEB5436}"/>
   </bookViews>
   <sheets>
     <sheet name="Part 1" sheetId="1" r:id="rId1"/>
     <sheet name="Part 2" sheetId="2" r:id="rId2"/>
-    <sheet name="Energy" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="53">
   <si>
     <t>Electrical Components</t>
   </si>
@@ -49,6 +51,9 @@
     <t>Total Cost</t>
   </si>
   <si>
+    <t>Lifespan</t>
+  </si>
+  <si>
     <t>1.5 MW Turbine (GE Vernova 1.5sle)</t>
   </si>
   <si>
@@ -85,13 +90,7 @@
     <t>Booster Pumps (Grundfos CR 10-10 K)</t>
   </si>
   <si>
-    <t>RO Membrane Trains</t>
-  </si>
-  <si>
-    <t>Calcite Bed Contactor (DrinTec FRP Calcite Contactor)</t>
-  </si>
-  <si>
-    <t>Multi-Media Filtration System (Pure Aqua MF-500 Series FRP Filter Skid)</t>
+    <t>Pure Aqua Large Reverse Osmosis System RO-600 (Includes Pre and Post treatment)</t>
   </si>
   <si>
     <t>Brine Disposal Well</t>
@@ -121,12 +120,12 @@
     <t>Variable-Displacement Hydraulic Power Unit (HPU)</t>
   </si>
   <si>
+    <t>300 Bar Hydraulic Manifold (Custom Ductile Iron Block)</t>
+  </si>
+  <si>
     <t>Note: likely will not be COTS, need custom engineering solutions for this scale</t>
   </si>
   <si>
-    <t>300 Bar Hydraulic Manifold (Custom Ductile Iron Block)</t>
-  </si>
-  <si>
     <t>Hydraulic Motor (225 kW rating) (Haaglund CA 50)</t>
   </si>
   <si>
@@ -145,49 +144,46 @@
     <t>Gate valve</t>
   </si>
   <si>
-    <t>Reverse osmosis train</t>
-  </si>
-  <si>
     <t>Extra storage tank (100,000 gallons)</t>
   </si>
   <si>
-    <t>Calcite bed contactors</t>
-  </si>
-  <si>
     <t>Pipes (total)</t>
   </si>
   <si>
     <t>Hybrid Components</t>
   </si>
   <si>
-    <t>Gearbox (Winergy PEAB series)</t>
-  </si>
-  <si>
-    <t>Variable-Displacement HPU</t>
-  </si>
-  <si>
-    <t>Hydraulic Motor (225 kW, Haaglund CA 50)</t>
-  </si>
-  <si>
-    <t>High Pressure Pump (Danfoss APP 78/1500 180B7808)</t>
-  </si>
-  <si>
-    <t>Battery (Tesla Megapack 3.9 MWh)</t>
-  </si>
-  <si>
-    <t>Booster Pump (Grundfos CR 10-10 K)</t>
-  </si>
-  <si>
-    <t>PLC (Siemens SIMATIC S7-1200 CPU1215C-1)</t>
-  </si>
-  <si>
-    <t>Multi-Media Filtration System (Pure Aqua MF-500 Series)</t>
-  </si>
-  <si>
-    <t>Reverse Osmosis Trains</t>
-  </si>
-  <si>
-    <t>Extra Storage Tank (100,000 gallons)</t>
+    <t>Gearbox (Winergy  PEAB series) - Must be ordered with second output shaft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCI544E 3-Phase - Stamford | 600 kW </t>
+  </si>
+  <si>
+    <t>Rectifier/Inverter Package</t>
+  </si>
+  <si>
+    <t>Energy Required for each subsystem</t>
+  </si>
+  <si>
+    <t>All the same, just configured differently due to different layouts</t>
+  </si>
+  <si>
+    <t>Groundwater extraction</t>
+  </si>
+  <si>
+    <t>172.9 kW</t>
+  </si>
+  <si>
+    <t>RO desalination</t>
+  </si>
+  <si>
+    <t>311.5 kW</t>
+  </si>
+  <si>
+    <t>Brine reinjection</t>
+  </si>
+  <si>
+    <t>81.9 kW</t>
   </si>
   <si>
     <t>TDS</t>
@@ -200,129 +196,6 @@
   </si>
   <si>
     <t>kW required (pump energy)</t>
-  </si>
-  <si>
-    <t>System / Subsystem</t>
-  </si>
-  <si>
-    <t>Shaft Power (kW)</t>
-  </si>
-  <si>
-    <t>Drive Type</t>
-  </si>
-  <si>
-    <t>Drivetrain Efficiency</t>
-  </si>
-  <si>
-    <t>Turbine Input (kW)</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Mechanical System</t>
-  </si>
-  <si>
-    <t>GW Extraction (Vertical Turbine Pump)</t>
-  </si>
-  <si>
-    <t>Hydraulic</t>
-  </si>
-  <si>
-    <t>hm x hpu x gb = 0.768</t>
-  </si>
-  <si>
-    <t>VTP driven by dedicated hydraulic motor</t>
-  </si>
-  <si>
-    <t>RO Feed Pressurization (High Pressure Pump)</t>
-  </si>
-  <si>
-    <t>Danfoss APP x3 driven by hydraulic motor</t>
-  </si>
-  <si>
-    <t>Brine Reinjection (Triplex Plunger Pump)</t>
-  </si>
-  <si>
-    <t>Plunger pump driven by hydraulic motor</t>
-  </si>
-  <si>
-    <t>Total Shaft Power</t>
-  </si>
-  <si>
-    <t>Total at Turbine Shaft</t>
-  </si>
-  <si>
-    <t>Design Power (+10% margin)</t>
-  </si>
-  <si>
-    <t>Selected Turbine (kW)</t>
-  </si>
-  <si>
-    <t>850 kW - next standard commercial above 810.8 kW design requirement</t>
-  </si>
-  <si>
-    <t>Electrical System</t>
-  </si>
-  <si>
-    <t>GW Extraction (Submersible Pump)</t>
-  </si>
-  <si>
-    <t>Electric motor</t>
-  </si>
-  <si>
-    <t>h_motor = 0.95</t>
-  </si>
-  <si>
-    <t>VFD-driven submersible; no HPU or gearbox losses</t>
-  </si>
-  <si>
-    <t>RO Feed Pressurization (Booster Pump)</t>
-  </si>
-  <si>
-    <t>Grundfos CR multi-stage; direct electric drive</t>
-  </si>
-  <si>
-    <t>Brine Disposal (Electric Pump to Well)</t>
-  </si>
-  <si>
-    <t>Electric pump to brine disposal well</t>
-  </si>
-  <si>
-    <t>Total Electrical Demand</t>
-  </si>
-  <si>
-    <t>Hybrid System</t>
-  </si>
-  <si>
-    <t>RO Feed Pressurization - hydraulic path (HP Pump)</t>
-  </si>
-  <si>
-    <t>HPU + hydraulic motor drives HP pump; highest-power load on hydraulic path</t>
-  </si>
-  <si>
-    <t>GW Extraction - electrical path (VTP)</t>
-  </si>
-  <si>
-    <t>h_motor x h_gen = 0.95 x 0.95 = 0.903</t>
-  </si>
-  <si>
-    <t>Turbine generator -&gt; battery -&gt; VTP motor</t>
-  </si>
-  <si>
-    <t>Brine Disposal - electrical path</t>
-  </si>
-  <si>
-    <t>Turbine generator -&gt; battery -&gt; disposal pump</t>
-  </si>
-  <si>
-    <t>Total at Turbine (hydraulic + electrical paths)</t>
-  </si>
-  <si>
-    <t>850 kW - same commercial platform as mechanical for consistency</t>
-  </si>
-  <si>
-    <t>1.5 MW GE Vernova 1.5sle - excess capacity charges battery for 24/7 continuous operations</t>
   </si>
 </sst>
 </file>
@@ -332,7 +205,7 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -399,12 +272,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF242424"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -412,47 +279,15 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <b/>
       <u/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -467,12 +302,38 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF156082"/>
+        <fgColor rgb="FFC0E6F5"/>
+        <bgColor auto="1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD6E4F0"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="65"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E6F5"/>
+        <bgColor rgb="FFC0E6F5"/>
       </patternFill>
     </fill>
   </fills>
@@ -509,25 +370,25 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="8" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="8" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="8" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="8" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="8" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="8" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="8" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="8" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="8" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -861,23 +722,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R50"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EB37D88-D019-4C24-B43B-C69173A467AF}">
+  <dimension ref="A1:R55"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="59.26953125" customWidth="1"/>
-    <col min="3" max="3" width="21.54296875" customWidth="1"/>
-    <col min="4" max="4" width="25.1796875" customWidth="1"/>
-    <col min="5" max="5" width="16.1796875" customWidth="1"/>
-    <col min="6" max="6" width="14.81640625" customWidth="1"/>
-    <col min="7" max="7" width="21.7265625" customWidth="1"/>
-    <col min="12" max="12" width="13.81640625" customWidth="1"/>
-    <col min="13" max="13" width="14.54296875" customWidth="1"/>
-    <col min="14" max="14" width="14.81640625" customWidth="1"/>
-    <col min="15" max="15" width="13.453125" customWidth="1"/>
-    <col min="16" max="16" width="16.1796875" customWidth="1"/>
-    <col min="17" max="17" width="13.1796875" customWidth="1"/>
-    <col min="18" max="18" width="10.54296875" customWidth="1"/>
+    <col min="2" max="2" width="59.28515625" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" customWidth="1"/>
+    <col min="4" max="4" width="25.140625" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" customWidth="1"/>
+    <col min="7" max="7" width="21.7109375" customWidth="1"/>
+    <col min="12" max="12" width="13.85546875" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" customWidth="1"/>
+    <col min="16" max="16" width="16.140625" customWidth="1"/>
+    <col min="17" max="17" width="13.140625" customWidth="1"/>
+    <col min="18" max="18" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="20.25" customHeight="1">
@@ -894,74 +755,86 @@
       <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" ht="14.5">
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="16">
-        <v>1</v>
-      </c>
-      <c r="D2" s="8">
+      <c r="B2" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="17">
+        <v>1</v>
+      </c>
+      <c r="D2" s="18">
         <v>1000000</v>
       </c>
-      <c r="E2" s="17">
-        <f t="shared" ref="E2:E11" si="0">D2*C2</f>
+      <c r="E2" s="19">
+        <f>D2*C2</f>
         <v>1000000</v>
+      </c>
+      <c r="F2">
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="15.75" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="16">
+      <c r="B3" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="20">
         <v>2</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="18">
         <v>2600</v>
       </c>
-      <c r="E3" s="17">
-        <f t="shared" si="0"/>
+      <c r="E3" s="19">
+        <f t="shared" ref="E3:E9" si="0">D3*C3</f>
         <v>5200</v>
       </c>
+      <c r="F3">
+        <v>15</v>
+      </c>
       <c r="L3" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="14.5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="16">
+        <v>14</v>
+      </c>
+      <c r="C4" s="21">
         <v>2</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="22">
         <v>200000</v>
       </c>
-      <c r="E4" s="17">
+      <c r="E4" s="14">
         <f t="shared" si="0"/>
         <v>400000</v>
+      </c>
+      <c r="F4">
+        <v>10</v>
       </c>
       <c r="L4" s="1">
         <v>0</v>
@@ -985,20 +858,23 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="14.5">
+    <row r="5" spans="1:18">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="16">
-        <v>1</v>
-      </c>
-      <c r="D5" s="9">
+        <v>15</v>
+      </c>
+      <c r="C5" s="13">
+        <v>1</v>
+      </c>
+      <c r="D5" s="22">
         <v>2600000</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="14">
         <f t="shared" si="0"/>
         <v>2600000</v>
+      </c>
+      <c r="F5">
+        <v>15</v>
       </c>
       <c r="L5" s="1">
         <v>0.1</v>
@@ -1022,20 +898,23 @@
         <v>260000</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="14.5">
+    <row r="6" spans="1:18">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="21">
+        <v>4</v>
+      </c>
+      <c r="D6" s="22">
+        <v>6000</v>
+      </c>
+      <c r="E6" s="14">
+        <f t="shared" si="0"/>
+        <v>24000</v>
+      </c>
+      <c r="F6">
         <v>15</v>
-      </c>
-      <c r="C6" s="16">
-        <v>4</v>
-      </c>
-      <c r="D6" s="9">
-        <v>6000</v>
-      </c>
-      <c r="E6" s="17">
-        <f t="shared" si="0"/>
-        <v>24000</v>
       </c>
       <c r="L6" s="1">
         <v>0.2</v>
@@ -1059,20 +938,23 @@
         <v>370000</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="14.5">
+    <row r="7" spans="1:18">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="16">
-        <v>2</v>
-      </c>
-      <c r="D7" s="9">
-        <v>3000000</v>
-      </c>
-      <c r="E7" s="17">
-        <f t="shared" si="0"/>
-        <v>6000000</v>
+        <v>17</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1</v>
+      </c>
+      <c r="D7" s="8">
+        <v>3500000</v>
+      </c>
+      <c r="E7" s="14">
+        <f t="shared" si="0"/>
+        <v>3500000</v>
+      </c>
+      <c r="F7">
+        <v>20</v>
       </c>
       <c r="L7" s="1">
         <v>0.3</v>
@@ -1096,20 +978,23 @@
         <v>480000</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="14.5">
+    <row r="8" spans="1:18">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="16">
-        <v>1</v>
-      </c>
-      <c r="D8" s="9">
-        <v>75000</v>
-      </c>
-      <c r="E8" s="17">
-        <f t="shared" si="0"/>
-        <v>75000</v>
+        <v>18</v>
+      </c>
+      <c r="C8" s="21">
+        <v>1</v>
+      </c>
+      <c r="D8" s="22">
+        <v>2300000</v>
+      </c>
+      <c r="E8" s="14">
+        <f t="shared" si="0"/>
+        <v>2300000</v>
+      </c>
+      <c r="F8">
+        <v>30</v>
       </c>
       <c r="L8" s="1">
         <v>0.4</v>
@@ -1133,20 +1018,23 @@
         <v>590000</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="14.5">
+    <row r="9" spans="1:18">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="16">
-        <v>2</v>
-      </c>
-      <c r="D9" s="9">
-        <v>15000</v>
-      </c>
-      <c r="E9" s="17">
-        <f t="shared" si="0"/>
-        <v>30000</v>
+        <v>19</v>
+      </c>
+      <c r="C9" s="13">
+        <v>1</v>
+      </c>
+      <c r="D9" s="22">
+        <v>2000000</v>
+      </c>
+      <c r="E9" s="14">
+        <f t="shared" si="0"/>
+        <v>2000000</v>
+      </c>
+      <c r="F9">
+        <v>30</v>
       </c>
       <c r="L9" s="1">
         <v>0.5</v>
@@ -1170,20 +1058,16 @@
         <v>700000</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="14.5">
+    <row r="10" spans="1:18">
       <c r="A10" s="1"/>
-      <c r="B10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="16">
-        <v>1</v>
-      </c>
-      <c r="D10" s="9">
-        <v>2300000</v>
-      </c>
-      <c r="E10" s="17">
-        <f t="shared" si="0"/>
-        <v>2300000</v>
+      <c r="B10" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="24"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="15">
+        <f>SUM(E2:E9)</f>
+        <v>11829200</v>
       </c>
       <c r="L10" s="1">
         <v>0.6</v>
@@ -1207,21 +1091,12 @@
         <v>810000</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="14.5">
+    <row r="11" spans="1:18">
       <c r="A11" s="1"/>
-      <c r="B11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="16">
-        <v>1</v>
-      </c>
-      <c r="D11" s="9">
-        <v>2000000</v>
-      </c>
-      <c r="E11" s="17">
-        <f t="shared" si="0"/>
-        <v>2000000</v>
-      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="15"/>
       <c r="L11" s="1">
         <v>0.7</v>
       </c>
@@ -1244,17 +1119,12 @@
         <v>920000</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="14.5">
+    <row r="12" spans="1:18">
       <c r="A12" s="3"/>
-      <c r="B12" s="3" t="s">
-        <v>21</v>
-      </c>
+      <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="18">
-        <f>SUM(E2:E11)</f>
-        <v>14434200</v>
-      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
       <c r="L12" s="1">
         <v>0.8</v>
       </c>
@@ -1277,7 +1147,7 @@
         <v>1030000</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="14.5">
+    <row r="13" spans="1:18">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -1307,12 +1177,20 @@
         <v>1140000</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="14.5">
+    <row r="14" spans="1:18">
       <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
+      <c r="B14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>4</v>
+      </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="L14" s="1">
@@ -1337,463 +1215,538 @@
         <v>1250000</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="14.5">
+    <row r="15" spans="1:18">
       <c r="A15" s="1"/>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="24">
+        <v>1</v>
+      </c>
+      <c r="D15" s="25">
+        <v>1000000</v>
+      </c>
+      <c r="E15" s="10">
+        <v>25</v>
+      </c>
+      <c r="F15" s="10"/>
+      <c r="G15" s="7"/>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="A16" s="1"/>
+      <c r="B16" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="24">
+        <v>3</v>
+      </c>
+      <c r="D16" s="25">
+        <v>15000</v>
+      </c>
+      <c r="E16" s="10">
+        <v>20</v>
+      </c>
+      <c r="F16" s="10"/>
+      <c r="G16" s="1"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="1">
+        <v>1</v>
+      </c>
+      <c r="D17" s="22">
+        <v>200000</v>
+      </c>
+      <c r="E17" s="10">
+        <v>20</v>
+      </c>
+      <c r="F17" s="10"/>
+      <c r="G17" s="1"/>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1</v>
+      </c>
+      <c r="D18" s="22">
+        <v>300000</v>
+      </c>
+      <c r="E18" s="10">
+        <v>15</v>
+      </c>
+      <c r="F18" s="10"/>
+      <c r="G18" s="1"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="1">
+        <v>1</v>
+      </c>
+      <c r="D19" s="22">
+        <v>20000</v>
+      </c>
+      <c r="E19" s="10">
+        <v>20</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="G19" s="1"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2</v>
+      </c>
+      <c r="D20" s="22">
+        <v>60000</v>
+      </c>
+      <c r="E20" s="10">
+        <v>15</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" s="1"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="1">
+        <v>1</v>
+      </c>
+      <c r="D21" s="22">
+        <v>50000</v>
+      </c>
+      <c r="E21" s="10">
+        <v>15</v>
+      </c>
+      <c r="F21" s="10"/>
+      <c r="G21" s="1"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="1">
+        <v>1</v>
+      </c>
+      <c r="D22" s="22">
+        <v>60000</v>
+      </c>
+      <c r="E22" s="10">
+        <v>15</v>
+      </c>
+      <c r="F22" s="10"/>
+      <c r="G22" s="1"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="1">
+        <v>1</v>
+      </c>
+      <c r="D23" s="22">
+        <v>35000</v>
+      </c>
+      <c r="E23" s="10">
+        <v>20</v>
+      </c>
+      <c r="F23" s="10"/>
+      <c r="G23" s="1"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="1">
+        <v>3</v>
+      </c>
+      <c r="D24" s="22">
+        <v>100000</v>
+      </c>
+      <c r="E24" s="10">
+        <v>15</v>
+      </c>
+      <c r="F24" s="10"/>
+      <c r="G24" s="1"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="1"/>
+      <c r="B25" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="24">
+        <v>2</v>
+      </c>
+      <c r="D25" s="25">
+        <v>8000</v>
+      </c>
+      <c r="E25" s="10">
+        <v>15</v>
+      </c>
+      <c r="F25" s="10"/>
+      <c r="G25" s="1"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="1">
+        <v>1</v>
+      </c>
+      <c r="D26" s="8">
+        <v>3500000</v>
+      </c>
+      <c r="E26" s="10">
+        <v>20</v>
+      </c>
+      <c r="F26" s="10"/>
+      <c r="G26" s="1"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2</v>
+      </c>
+      <c r="D27" s="8">
+        <v>140000</v>
+      </c>
+      <c r="E27" s="10">
+        <v>30</v>
+      </c>
+      <c r="F27" s="10"/>
+      <c r="G27" s="1"/>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="1"/>
+      <c r="B28" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="24"/>
+      <c r="D28" s="25">
+        <v>2000000</v>
+      </c>
+      <c r="E28" s="10">
+        <v>30</v>
+      </c>
+      <c r="F28" s="10"/>
+      <c r="G28" s="1"/>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="1"/>
+      <c r="B29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" s="3"/>
+      <c r="D29" s="26">
+        <f>SUM(D15:D27)</f>
+        <v>5488000</v>
+      </c>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="1"/>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="3"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="3"/>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="1"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="1"/>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="1"/>
+      <c r="B32" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D32" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D15" s="10" t="s">
+      <c r="E32" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="10"/>
+      <c r="G32" s="1"/>
+    </row>
+    <row r="33" spans="2:6">
+      <c r="B33" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="7"/>
-    </row>
-    <row r="16" spans="1:18" ht="14.5">
-      <c r="A16" s="1"/>
-      <c r="B16" s="11" t="s">
+      <c r="C33" s="24">
+        <v>1</v>
+      </c>
+      <c r="D33" s="25">
+        <v>1000000</v>
+      </c>
+      <c r="E33">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6">
+      <c r="B34" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="11">
-        <v>1</v>
-      </c>
-      <c r="D16" s="14">
-        <v>1000000</v>
-      </c>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="1"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.5">
-      <c r="A17" s="1"/>
-      <c r="B17" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="11">
+      <c r="C34" s="24">
         <v>3</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D34" s="25">
         <v>15000</v>
       </c>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="1"/>
-    </row>
-    <row r="18" spans="1:7" ht="14.5">
-      <c r="A18" s="1"/>
-      <c r="B18" s="11" t="s">
+      <c r="E34">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6">
+      <c r="B35" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C35" s="1">
+        <v>1</v>
+      </c>
+      <c r="D35" s="22">
+        <v>200000</v>
+      </c>
+      <c r="E35">
+        <v>20</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6">
+      <c r="B36" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="11">
-        <v>1</v>
-      </c>
-      <c r="D18" s="15">
+      <c r="C36" s="1">
+        <v>1</v>
+      </c>
+      <c r="D36" s="22">
+        <v>300000</v>
+      </c>
+      <c r="E36">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6">
+      <c r="B37" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" s="1">
+        <v>1</v>
+      </c>
+      <c r="D37" s="22">
+        <v>50000</v>
+      </c>
+      <c r="E37">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6">
+      <c r="B38" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C38" s="1">
+        <v>1</v>
+      </c>
+      <c r="D38" s="22">
+        <v>60000</v>
+      </c>
+      <c r="E38">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6">
+      <c r="B39" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C39" s="1">
+        <v>2</v>
+      </c>
+      <c r="D39" s="8">
+        <v>140000</v>
+      </c>
+      <c r="E39">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6">
+      <c r="B40" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="C40" s="24"/>
+      <c r="D40" s="25">
+        <v>2000000</v>
+      </c>
+      <c r="E40">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="2:6">
+      <c r="B41" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="20">
+        <v>2</v>
+      </c>
+      <c r="D41" s="18">
+        <v>5200</v>
+      </c>
+      <c r="E41">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6">
+      <c r="B42" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C42" s="13">
+        <v>1</v>
+      </c>
+      <c r="D42" s="22">
+        <v>2600000</v>
+      </c>
+      <c r="E42">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6">
+      <c r="B43" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C43" s="1">
+        <v>1</v>
+      </c>
+      <c r="D43" s="8">
+        <v>3500000</v>
+      </c>
+      <c r="E43">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6">
+      <c r="B44" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C44" s="1">
+        <v>3</v>
+      </c>
+      <c r="D44" s="22">
+        <v>100000</v>
+      </c>
+      <c r="E44">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6">
+      <c r="B45" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C45" s="1">
+        <v>1</v>
+      </c>
+      <c r="D45" s="22">
         <v>200000</v>
       </c>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="1"/>
-    </row>
-    <row r="19" spans="1:7" ht="14.5">
-      <c r="A19" s="1"/>
-      <c r="B19" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="11">
-        <v>1</v>
-      </c>
-      <c r="D19" s="15">
-        <v>300000</v>
-      </c>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="G19" s="1"/>
-    </row>
-    <row r="20" spans="1:7" ht="14.5">
-      <c r="A20" s="1"/>
-      <c r="B20" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" s="11">
-        <v>1</v>
-      </c>
-      <c r="D20" s="15">
-        <v>20000</v>
-      </c>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="G20" s="1"/>
-    </row>
-    <row r="21" spans="1:7" ht="14.5">
-      <c r="A21" s="1"/>
-      <c r="B21" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" s="11">
-        <v>2</v>
-      </c>
-      <c r="D21" s="15">
+      <c r="E45">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6" ht="15" customHeight="1">
+      <c r="B46" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C46" s="1">
+        <v>1</v>
+      </c>
+      <c r="D46" s="22">
         <v>60000</v>
       </c>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="1"/>
-    </row>
-    <row r="22" spans="1:7" ht="14.5">
-      <c r="A22" s="1"/>
-      <c r="B22" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22" s="11">
-        <v>1</v>
-      </c>
-      <c r="D22" s="15">
-        <v>50000</v>
-      </c>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="1"/>
-    </row>
-    <row r="23" spans="1:7" ht="14.5">
-      <c r="A23" s="1"/>
-      <c r="B23" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" s="11">
-        <v>1</v>
-      </c>
-      <c r="D23" s="15">
-        <v>60000</v>
-      </c>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="1"/>
-    </row>
-    <row r="24" spans="1:7" ht="14.5">
-      <c r="A24" s="1"/>
-      <c r="B24" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" s="11">
-        <v>1</v>
-      </c>
-      <c r="D24" s="15">
-        <v>35000</v>
-      </c>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="1"/>
-    </row>
-    <row r="25" spans="1:7" ht="14.5">
-      <c r="A25" s="1"/>
-      <c r="B25" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" s="11">
-        <v>3</v>
-      </c>
-      <c r="D25" s="15">
-        <v>100000</v>
-      </c>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="1"/>
-    </row>
-    <row r="26" spans="1:7" ht="14.5">
-      <c r="A26" s="1"/>
-      <c r="B26" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C26" s="11">
-        <v>2</v>
-      </c>
-      <c r="D26" s="14">
-        <v>8000</v>
-      </c>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="1"/>
-    </row>
-    <row r="27" spans="1:7" ht="14.5">
-      <c r="A27" s="1"/>
-      <c r="B27" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C27" s="11">
-        <v>2</v>
-      </c>
-      <c r="D27" s="14">
-        <v>7570000</v>
-      </c>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="1"/>
-    </row>
-    <row r="28" spans="1:7" ht="14.5">
-      <c r="A28" s="1"/>
-      <c r="B28" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C28" s="11">
-        <v>2</v>
-      </c>
-      <c r="D28" s="14">
-        <v>140000</v>
-      </c>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="1"/>
-    </row>
-    <row r="29" spans="1:7" ht="14.5">
-      <c r="A29" s="1"/>
-      <c r="B29" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C29" s="11">
-        <v>2</v>
-      </c>
-      <c r="D29" s="14">
-        <v>100000</v>
-      </c>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="1"/>
-    </row>
-    <row r="30" spans="1:7" ht="14.5">
-      <c r="A30" s="3"/>
-      <c r="B30" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C30" s="11"/>
-      <c r="D30" s="14">
-        <v>2000000</v>
-      </c>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="3"/>
-    </row>
-    <row r="31" spans="1:7" ht="14.5">
-      <c r="A31" s="1"/>
-      <c r="B31" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C31" s="12"/>
-      <c r="D31" s="13">
-        <v>9658000</v>
-      </c>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="1"/>
-    </row>
-    <row r="32" spans="1:7" ht="14.5">
-      <c r="A32" s="1"/>
-      <c r="B32" s="12"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="1"/>
-    </row>
-    <row r="33" spans="2:4" ht="14.5">
-      <c r="B33" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4" ht="14.5">
-      <c r="B34" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C34" s="19">
-        <v>1</v>
-      </c>
-      <c r="D34" s="19">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4" ht="14.5">
-      <c r="B35" s="19" t="s">
+      <c r="E46">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6" ht="15" customHeight="1">
+      <c r="B47" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D47" s="15">
+        <f>SUM(D33:D44)</f>
+        <v>9970200</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" ht="15" customHeight="1">
+      <c r="B51" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C35" s="19">
-        <v>1</v>
-      </c>
-      <c r="D35" s="19">
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4" ht="14.5">
-      <c r="B36" s="19" t="s">
+      <c r="C51" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="C36" s="19">
-        <v>1</v>
-      </c>
-      <c r="D36" s="19">
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4" ht="14.5">
-      <c r="B37" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="C37" s="19">
-        <v>1</v>
-      </c>
-      <c r="D37" s="19">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4" ht="14.5">
-      <c r="B38" s="19" t="s">
+      <c r="D51" s="27"/>
+      <c r="E51" s="27"/>
+    </row>
+    <row r="52" spans="2:5" ht="15" customHeight="1">
+      <c r="B52" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="C38" s="19">
-        <v>1</v>
-      </c>
-      <c r="D38" s="19">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4" ht="14.5">
-      <c r="B39" s="19" t="s">
+      <c r="C52" t="s">
         <v>44</v>
       </c>
-      <c r="C39" s="19">
-        <v>1</v>
-      </c>
-      <c r="D39" s="19">
-        <v>35000</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4" ht="14.5">
-      <c r="B40" s="19" t="s">
+    </row>
+    <row r="53" spans="2:5" ht="15" customHeight="1">
+      <c r="B53" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="C40" s="19">
-        <v>1</v>
-      </c>
-      <c r="D40" s="19">
-        <v>2600000</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4" ht="14.5">
-      <c r="B41" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="C41" s="19">
-        <v>1</v>
-      </c>
-      <c r="D41" s="19">
-        <v>60000</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4" ht="14.5">
-      <c r="B42" s="19" t="s">
+      <c r="C53" t="s">
         <v>46</v>
       </c>
-      <c r="C42" s="19">
-        <v>2</v>
-      </c>
-      <c r="D42" s="19">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4" ht="14.5">
-      <c r="B43" s="19" t="s">
+    </row>
+    <row r="54" spans="2:5" ht="15" customHeight="1">
+      <c r="B54" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C43" s="19">
-        <v>1</v>
-      </c>
-      <c r="D43" s="19">
-        <v>2600</v>
-      </c>
-    </row>
-    <row r="44" spans="2:4" ht="14.5">
-      <c r="B44" s="19" t="s">
+      <c r="C54" t="s">
         <v>48</v>
       </c>
-      <c r="C44" s="19">
-        <v>1</v>
-      </c>
-      <c r="D44" s="19">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="45" spans="2:4" ht="14.5">
-      <c r="B45" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="C45" s="19">
-        <v>2</v>
-      </c>
-      <c r="D45" s="19">
-        <v>7570000</v>
-      </c>
-    </row>
-    <row r="46" spans="2:4" ht="14.5">
-      <c r="B46" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C46" s="19">
-        <v>1</v>
-      </c>
-      <c r="D46" s="19">
-        <v>75000</v>
-      </c>
-    </row>
-    <row r="47" spans="2:4" ht="14.5">
-      <c r="B47" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="C47" s="19">
-        <v>1</v>
-      </c>
-      <c r="D47" s="19">
-        <v>2300000</v>
-      </c>
-    </row>
-    <row r="48" spans="2:4" ht="14.5">
-      <c r="B48" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="C48" s="19">
-        <v>2</v>
-      </c>
-      <c r="D48" s="19">
-        <v>140000</v>
-      </c>
-    </row>
-    <row r="49" spans="2:4" ht="14.5">
-      <c r="B49" s="19" t="s">
+    </row>
+    <row r="55" spans="2:5" ht="15" customHeight="1">
+      <c r="B55" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="C49" s="19"/>
-      <c r="D49" s="19">
-        <v>2000000</v>
-      </c>
-    </row>
-    <row r="50" spans="2:4" ht="14.5">
-      <c r="B50" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="C50" s="20"/>
-      <c r="D50" s="20">
-        <f>SUM(D34:D49)</f>
-        <v>16359600</v>
       </c>
     </row>
   </sheetData>
@@ -1802,25 +1755,25 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C39F0B8-8C3B-42AE-9AF7-8CD4FC164E71}">
   <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="6.81640625" customWidth="1"/>
+    <col min="3" max="3" width="6.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>52</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1828,14 +1781,14 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <f t="shared" ref="B2:B21" si="0">0.0146053*A2 + 630.72</f>
+        <f>0.0146053*A2 + 630.72</f>
         <v>630.72</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <f t="shared" ref="E2:E21" si="1">0.5725*D2</f>
+        <f>0.5725*D2</f>
         <v>0</v>
       </c>
     </row>
@@ -1844,14 +1797,14 @@
         <v>100</v>
       </c>
       <c r="B3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B3:B21" si="0">0.0146053*A3 + 630.72</f>
         <v>632.18052999999998</v>
       </c>
       <c r="D3">
         <v>100</v>
       </c>
       <c r="E3">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="E3:E21" si="1">0.5725*D3</f>
         <v>57.25</v>
       </c>
     </row>
@@ -2146,368 +2099,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F29"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <cols>
-    <col min="1" max="1" width="46" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="54" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1" s="24" t="s">
-        <v>57</v>
-      </c>
-      <c r="D1" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="F1" s="24" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="B3" s="19">
-        <v>172.9</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="E3" s="19">
-        <v>225.1</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="B4" s="19">
-        <v>311.49</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="E4" s="19">
-        <v>405.5</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="B5" s="19">
-        <v>81.864999999999995</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="E5" s="19">
-        <v>106.6</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="B6" s="20">
-        <v>566.255</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="E7" s="20">
-        <v>737.1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" s="20">
-        <v>810.8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="E9" s="20">
-        <v>850</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="B12" s="19">
-        <v>172.9</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="E12" s="19">
-        <v>182</v>
-      </c>
-      <c r="F12" s="19" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="B13" s="19">
-        <v>311.49</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="E13" s="19">
-        <v>327.9</v>
-      </c>
-      <c r="F13" s="19" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="B14" s="19">
-        <v>81.864999999999995</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="E14" s="19">
-        <v>86.2</v>
-      </c>
-      <c r="F14" s="19" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="B15" s="20">
-        <v>566.255</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="E16" s="20">
-        <v>596.1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="E17" s="20">
-        <v>655.7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="E18" s="20">
-        <v>1500</v>
-      </c>
-      <c r="F18" s="25" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="B20" s="21"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="B21" s="19">
-        <v>311.49</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="D21" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="E21" s="19">
-        <v>405.5</v>
-      </c>
-      <c r="F21" s="19" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="B22" s="19">
-        <v>172.9</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="E22" s="19">
-        <v>191.6</v>
-      </c>
-      <c r="F22" s="19" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="B23" s="19">
-        <v>81.864999999999995</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="D23" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="E23" s="19">
-        <v>90.7</v>
-      </c>
-      <c r="F23" s="19" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="B24" s="20">
-        <v>566.255</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="E25" s="20">
-        <v>687.7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="E26" s="20">
-        <v>756.5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="E27" s="20">
-        <v>850</v>
-      </c>
-      <c r="F27" s="25" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="26"/>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A29:F29"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kevin\Downloads\Desalination Project Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84CE319F-3F78-4C7C-8DCF-F97A46A95F68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D32C5533-DC74-4D19-AA89-DB2A0E81D5CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Part 1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="57">
   <si>
     <t>Electrical Components</t>
   </si>
@@ -199,6 +199,12 @@
   </si>
   <si>
     <t>kW delta (pump energy) from design [depth=275 m]</t>
+  </si>
+  <si>
+    <t>Brine Disposal Well</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
 </sst>
 </file>
@@ -727,7 +733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R55"/>
+  <dimension ref="A1:R58"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="59.26953125" customWidth="1"/>
@@ -775,7 +781,7 @@
         <v>1000000</v>
       </c>
       <c r="E2" s="19">
-        <f t="shared" ref="E2:E8" si="0">D2*C2</f>
+        <f t="shared" ref="E2:E9" si="0">D2*C2</f>
         <v>1000000</v>
       </c>
       <c r="F2">
@@ -948,14 +954,14 @@
         <v>17</v>
       </c>
       <c r="C7" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" s="8">
         <v>3500000</v>
       </c>
       <c r="E7" s="14">
         <f t="shared" si="0"/>
-        <v>7000000</v>
+        <v>3500000</v>
       </c>
       <c r="F7">
         <v>20</v>
@@ -985,244 +991,253 @@
     <row r="8" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="13">
-        <v>1</v>
-      </c>
-      <c r="D8" s="22">
-        <v>2000000</v>
+        <v>55</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1</v>
+      </c>
+      <c r="D8" s="8">
+        <v>2300000</v>
       </c>
       <c r="E8" s="14">
         <f t="shared" si="0"/>
-        <v>2000000</v>
-      </c>
-      <c r="F8">
-        <v>30</v>
-      </c>
-      <c r="L8" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="M8" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="N8" s="4">
-        <v>5000</v>
-      </c>
-      <c r="O8" s="4">
-        <v>500000</v>
-      </c>
-      <c r="P8" s="4">
-        <v>625000</v>
-      </c>
-      <c r="Q8" s="4">
-        <v>75000</v>
-      </c>
-      <c r="R8" s="4">
-        <v>700000</v>
-      </c>
+        <v>2300000</v>
+      </c>
+      <c r="F8" t="s">
+        <v>56</v>
+      </c>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
     </row>
     <row r="9" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A9" s="1"/>
-      <c r="B9" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="24"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="15">
-        <f>SUM(E2:E8)</f>
-        <v>13029200</v>
+      <c r="B9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="13">
+        <v>1</v>
+      </c>
+      <c r="D9" s="22">
+        <v>2000000</v>
+      </c>
+      <c r="E9" s="14">
+        <f t="shared" si="0"/>
+        <v>2000000</v>
+      </c>
+      <c r="F9">
+        <v>30</v>
       </c>
       <c r="L9" s="1">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="M9" s="1">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="N9" s="4">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="O9" s="4">
-        <v>400000</v>
+        <v>500000</v>
       </c>
       <c r="P9" s="4">
-        <v>750000</v>
+        <v>625000</v>
       </c>
       <c r="Q9" s="4">
-        <v>60000</v>
+        <v>75000</v>
       </c>
       <c r="R9" s="4">
-        <v>810000</v>
+        <v>700000</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A10" s="1"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="15"/>
+      <c r="B10" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="24"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="15">
+        <f>SUM(E2:E9)</f>
+        <v>11829200</v>
+      </c>
       <c r="L10" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="M10" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="N10" s="4">
+        <v>6000</v>
+      </c>
+      <c r="O10" s="4">
+        <v>400000</v>
+      </c>
+      <c r="P10" s="4">
+        <v>750000</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>60000</v>
+      </c>
+      <c r="R10" s="4">
+        <v>810000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="1"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="15"/>
+      <c r="L11" s="1">
         <v>0.7</v>
       </c>
-      <c r="M10" s="1">
+      <c r="M11" s="1">
         <v>0.3</v>
       </c>
-      <c r="N10" s="4">
+      <c r="N11" s="4">
         <v>7000</v>
       </c>
-      <c r="O10" s="4">
+      <c r="O11" s="4">
         <v>300000</v>
       </c>
-      <c r="P10" s="4">
+      <c r="P11" s="4">
         <v>875000</v>
       </c>
-      <c r="Q10" s="4">
+      <c r="Q11" s="4">
         <v>45000</v>
       </c>
-      <c r="R10" s="4">
+      <c r="R11" s="4">
         <v>920000</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="3"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="L11" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="M11" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="N11" s="4">
-        <v>8000</v>
-      </c>
-      <c r="O11" s="4">
-        <v>200000</v>
-      </c>
-      <c r="P11" s="4">
-        <v>1000000</v>
-      </c>
-      <c r="Q11" s="4">
-        <v>30000</v>
-      </c>
-      <c r="R11" s="4">
-        <v>1030000</v>
-      </c>
-    </row>
     <row r="12" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="1"/>
+      <c r="A12" s="3"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
       <c r="L12" s="1">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="M12" s="1">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="N12" s="4">
-        <v>9000</v>
+        <v>8000</v>
       </c>
       <c r="O12" s="4">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="P12" s="4">
-        <v>1125000</v>
+        <v>1000000</v>
       </c>
       <c r="Q12" s="4">
-        <v>15000</v>
+        <v>30000</v>
       </c>
       <c r="R12" s="4">
-        <v>1140000</v>
+        <v>1030000</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A13" s="1"/>
-      <c r="B13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>4</v>
-      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="L13" s="1">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="M13" s="1">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N13" s="4">
-        <v>10000</v>
-      </c>
-      <c r="O13" s="1">
-        <v>0</v>
+        <v>9000</v>
+      </c>
+      <c r="O13" s="4">
+        <v>100000</v>
       </c>
       <c r="P13" s="4">
-        <v>1250000</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>0</v>
+        <v>1125000</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>15000</v>
       </c>
       <c r="R13" s="4">
-        <v>1250000</v>
+        <v>1140000</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A14" s="1"/>
-      <c r="B14" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="24">
-        <v>1</v>
-      </c>
-      <c r="D14" s="25">
-        <v>1000000</v>
-      </c>
-      <c r="E14" s="10">
-        <v>25</v>
-      </c>
-      <c r="F14" s="10"/>
-      <c r="G14" s="7"/>
+      <c r="B14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="L14" s="1">
+        <v>1</v>
+      </c>
+      <c r="M14" s="1">
+        <v>0</v>
+      </c>
+      <c r="N14" s="4">
+        <v>10000</v>
+      </c>
+      <c r="O14" s="1">
+        <v>0</v>
+      </c>
+      <c r="P14" s="4">
+        <v>1250000</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>0</v>
+      </c>
+      <c r="R14" s="4">
+        <v>1250000</v>
+      </c>
     </row>
     <row r="15" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A15" s="1"/>
       <c r="B15" s="24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C15" s="24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D15" s="25">
-        <v>15000</v>
+        <v>1000000</v>
       </c>
       <c r="E15" s="10">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F15" s="10"/>
-      <c r="G15" s="1"/>
+      <c r="G15" s="7"/>
     </row>
     <row r="16" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
-      <c r="B16" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="1">
-        <v>1</v>
-      </c>
-      <c r="D16" s="22">
-        <v>200000</v>
+      <c r="B16" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="24">
+        <v>3</v>
+      </c>
+      <c r="D16" s="25">
+        <v>15000</v>
       </c>
       <c r="E16" s="10">
         <v>20</v>
@@ -1233,16 +1248,16 @@
     <row r="17" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
       <c r="B17" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C17" s="1">
         <v>1</v>
       </c>
       <c r="D17" s="22">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="E17" s="10">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F17" s="10"/>
       <c r="G17" s="1"/>
@@ -1250,35 +1265,33 @@
     <row r="18" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C18" s="1">
         <v>1</v>
       </c>
       <c r="D18" s="22">
-        <v>20000</v>
+        <v>300000</v>
       </c>
       <c r="E18" s="10">
-        <v>20</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>27</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="F18" s="10"/>
       <c r="G18" s="1"/>
     </row>
     <row r="19" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C19" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" s="22">
-        <v>60000</v>
+        <v>20000</v>
       </c>
       <c r="E19" s="10">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>27</v>
@@ -1288,30 +1301,32 @@
     <row r="20" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A20" s="1"/>
       <c r="B20" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="22">
-        <v>50000</v>
+        <v>60000</v>
       </c>
       <c r="E20" s="10">
         <v>15</v>
       </c>
-      <c r="F20" s="10"/>
+      <c r="F20" s="10" t="s">
+        <v>27</v>
+      </c>
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A21" s="1"/>
       <c r="B21" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21" s="1">
         <v>1</v>
       </c>
       <c r="D21" s="22">
-        <v>60000</v>
+        <v>50000</v>
       </c>
       <c r="E21" s="10">
         <v>15</v>
@@ -1322,16 +1337,16 @@
     <row r="22" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C22" s="1">
         <v>1</v>
       </c>
       <c r="D22" s="22">
-        <v>35000</v>
+        <v>60000</v>
       </c>
       <c r="E22" s="10">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="1"/>
@@ -1339,30 +1354,30 @@
     <row r="23" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
       <c r="B23" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D23" s="22">
-        <v>100000</v>
+        <v>35000</v>
       </c>
       <c r="E23" s="10">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="1"/>
     </row>
     <row r="24" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
-      <c r="B24" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" s="24">
-        <v>2</v>
-      </c>
-      <c r="D24" s="25">
-        <v>8000</v>
+      <c r="B24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="1">
+        <v>3</v>
+      </c>
+      <c r="D24" s="22">
+        <v>100000</v>
       </c>
       <c r="E24" s="10">
         <v>15</v>
@@ -1372,17 +1387,17 @@
     </row>
     <row r="25" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
-      <c r="B25" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C25" s="1">
+      <c r="B25" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="24">
         <v>2</v>
       </c>
-      <c r="D25" s="8">
-        <v>7000000</v>
+      <c r="D25" s="25">
+        <v>8000</v>
       </c>
       <c r="E25" s="10">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F25" s="10"/>
       <c r="G25" s="1"/>
@@ -1390,28 +1405,30 @@
     <row r="26" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A26" s="1"/>
       <c r="B26" s="1" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C26" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" s="8">
-        <v>140000</v>
+        <v>3500000</v>
       </c>
       <c r="E26" s="10">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F26" s="10"/>
       <c r="G26" s="1"/>
     </row>
     <row r="27" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A27" s="1"/>
-      <c r="B27" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" s="24"/>
-      <c r="D27" s="25">
-        <v>2000000</v>
+      <c r="B27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2</v>
+      </c>
+      <c r="D27" s="8">
+        <v>140000</v>
       </c>
       <c r="E27" s="10">
         <v>30</v>
@@ -1420,307 +1437,353 @@
       <c r="G27" s="1"/>
     </row>
     <row r="28" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="1"/>
-      <c r="B28" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="26">
-        <f>SUM(D14:D27)</f>
-        <v>10988000</v>
-      </c>
-      <c r="E28" s="10"/>
+      <c r="A28" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" s="1">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
+        <v>2300000</v>
+      </c>
+      <c r="E28" t="s">
+        <v>56</v>
+      </c>
       <c r="F28" s="10"/>
       <c r="G28" s="1"/>
     </row>
     <row r="29" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="3"/>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="10"/>
+      <c r="A29" s="1"/>
+      <c r="B29" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="24"/>
+      <c r="D29" s="25">
+        <v>2000000</v>
+      </c>
+      <c r="E29" s="10">
+        <v>30</v>
+      </c>
       <c r="F29" s="10"/>
-      <c r="G29" s="3"/>
+      <c r="G29" s="1"/>
     </row>
     <row r="30" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A30" s="1"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="12"/>
+      <c r="B30" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" s="3"/>
+      <c r="D30" s="26">
+        <f>SUM(D15:D29)</f>
+        <v>9788000</v>
+      </c>
       <c r="E30" s="10"/>
       <c r="F30" s="10"/>
-      <c r="G30" s="1"/>
+      <c r="G30" s="3"/>
     </row>
     <row r="31" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A31" s="1"/>
-      <c r="B31" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>4</v>
-      </c>
+      <c r="A31" s="3"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="10"/>
       <c r="F31" s="10"/>
       <c r="G31" s="1"/>
     </row>
     <row r="32" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B32" s="24" t="s">
+      <c r="A32" s="1"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="1"/>
+    </row>
+    <row r="33" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="1"/>
+      <c r="B33" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B34" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="C32" s="24">
-        <v>1</v>
-      </c>
-      <c r="D32" s="25">
+      <c r="C34" s="24">
+        <v>1</v>
+      </c>
+      <c r="D34" s="25">
         <v>1000000</v>
       </c>
-      <c r="E32">
+      <c r="E34">
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="2:6" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B33" s="24" t="s">
+    <row r="35" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B35" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="C33" s="24">
+      <c r="C35" s="24">
         <v>3</v>
       </c>
-      <c r="D33" s="25">
+      <c r="D35" s="25">
         <v>15000</v>
       </c>
-      <c r="E33">
+      <c r="E35">
         <v>20</v>
       </c>
-    </row>
-    <row r="34" spans="2:6" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B34" s="1" t="s">
+      <c r="F35" s="10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B36" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C34" s="1">
-        <v>1</v>
-      </c>
-      <c r="D34" s="22">
+      <c r="C36" s="1">
+        <v>1</v>
+      </c>
+      <c r="D36" s="22">
         <v>200000</v>
       </c>
-      <c r="E34">
+      <c r="E36">
         <v>20</v>
       </c>
-      <c r="F34" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="35" spans="2:6" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B35" s="1" t="s">
+    </row>
+    <row r="37" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B37" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C35" s="1">
-        <v>1</v>
-      </c>
-      <c r="D35" s="22">
+      <c r="C37" s="1">
+        <v>1</v>
+      </c>
+      <c r="D37" s="22">
         <v>300000</v>
-      </c>
-      <c r="E35">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" spans="2:6" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B36" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C36" s="1">
-        <v>1</v>
-      </c>
-      <c r="D36" s="22">
-        <v>50000</v>
-      </c>
-      <c r="E36">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37" spans="2:6" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B37" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C37" s="1">
-        <v>1</v>
-      </c>
-      <c r="D37" s="22">
-        <v>60000</v>
       </c>
       <c r="E37">
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="2:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B38" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="1">
+        <v>1</v>
+      </c>
+      <c r="D38" s="22">
+        <v>50000</v>
+      </c>
+      <c r="E38">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B39" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C39" s="1">
+        <v>1</v>
+      </c>
+      <c r="D39" s="22">
+        <v>60000</v>
+      </c>
+      <c r="E39">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B40" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C38" s="1">
+      <c r="C40" s="1">
         <v>2</v>
       </c>
-      <c r="D38" s="8">
+      <c r="D40" s="8">
         <v>140000</v>
       </c>
-      <c r="E38">
+      <c r="E40">
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="2:6" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B39" s="24" t="s">
+    <row r="41" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B41" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="C39" s="24"/>
-      <c r="D39" s="25">
+      <c r="C41" s="24"/>
+      <c r="D41" s="25">
         <v>2000000</v>
       </c>
-      <c r="E39">
+      <c r="E41">
         <v>30</v>
       </c>
     </row>
-    <row r="40" spans="2:6" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B40" s="16" t="s">
+    <row r="42" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B42" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C40" s="20">
+      <c r="C42" s="20">
         <v>2</v>
       </c>
-      <c r="D40" s="18">
+      <c r="D42" s="18">
         <v>5200</v>
       </c>
-      <c r="E40">
+      <c r="E42">
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="2:6" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B41" s="1" t="s">
+    <row r="43" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B43" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C41" s="13">
-        <v>1</v>
-      </c>
-      <c r="D41" s="22">
+      <c r="C43" s="13">
+        <v>1</v>
+      </c>
+      <c r="D43" s="22">
         <v>2600000</v>
-      </c>
-      <c r="E41">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="42" spans="2:6" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B42" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C42" s="1">
-        <v>2</v>
-      </c>
-      <c r="D42" s="8">
-        <v>7000000</v>
-      </c>
-      <c r="E42">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="43" spans="2:6" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B43" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C43" s="1">
-        <v>3</v>
-      </c>
-      <c r="D43" s="22">
-        <v>100000</v>
       </c>
       <c r="E43">
         <v>15</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B44" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="C44" s="1">
         <v>1</v>
       </c>
-      <c r="D44" s="22">
-        <v>200000</v>
+      <c r="D44" s="8">
+        <v>3500000</v>
       </c>
       <c r="E44">
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B45" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C45" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D45" s="22">
-        <v>60000</v>
+        <v>100000</v>
       </c>
       <c r="E45">
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B46" s="6" t="s">
+    <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B46" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="1">
+        <v>1</v>
+      </c>
+      <c r="D46" s="22">
+        <v>200000</v>
+      </c>
+      <c r="E46">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B47" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C47" s="1">
+        <v>1</v>
+      </c>
+      <c r="D47" s="14">
+        <v>2300000</v>
+      </c>
+      <c r="E47" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B48" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="1">
+        <v>1</v>
+      </c>
+      <c r="D48" s="22">
+        <v>60000</v>
+      </c>
+      <c r="E48">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B49" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D46" s="15">
-        <f>SUM(D32:D45)</f>
-        <v>13730200</v>
-      </c>
-    </row>
-    <row r="50" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="6" t="s">
+      <c r="D49" s="15">
+        <f>SUM(D34:D48)</f>
+        <v>12530200</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B53" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="27" t="s">
+      <c r="C53" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="D50" s="27"/>
-      <c r="E50" s="27"/>
-    </row>
-    <row r="51" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="27" t="s">
+      <c r="D53" s="27"/>
+      <c r="E53" s="27"/>
+    </row>
+    <row r="54" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B54" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C54" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="52" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="27" t="s">
+    <row r="55" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B55" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C55" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="53" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="27" t="s">
+    <row r="56" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B56" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C56" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="54" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="5" t="s">
+    <row r="57" spans="2:5" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B57" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C57" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="55" spans="2:5" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B55" t="s">
+    <row r="58" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B58" t="s">
         <v>19</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C58" t="s">
         <v>50</v>
       </c>
     </row>
